--- a/filer/25834844_fertin.xlsx
+++ b/filer/25834844_fertin.xlsx
@@ -7475,7 +7475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7582,24 +7582,22 @@
       </c>
       <c r="B4" s="37" t="inlineStr">
         <is>
-          <t>fsa:ImpairmentLossesOfIntangibleAssets</t>
+          <t>fsa:RaisingOfDebtToAssociates</t>
         </is>
       </c>
       <c r="C4" s="37" t="inlineStr">
         <is>
-          <t>fsa:ImpairmentLossesOfIntangibleAssets</t>
-        </is>
-      </c>
-      <c r="D4" s="38" t="n"/>
+          <t>fsa:RaisingOfDebtToAssociates</t>
+        </is>
+      </c>
+      <c r="D4" s="38" t="n">
+        <v>-22495</v>
+      </c>
       <c r="E4" s="38" t="n">
-        <v>23585</v>
-      </c>
-      <c r="F4" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="38" t="n">
-        <v>-15175</v>
-      </c>
+      <c r="F4" s="38" t="n"/>
+      <c r="G4" s="38" t="n"/>
       <c r="H4" s="38" t="n"/>
       <c r="I4" s="39" t="inlineStr">
         <is>
@@ -7615,23 +7613,21 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>fsa:RaisingOfDebtToAssociates</t>
+          <t>fsa:RefundInJointAssessment</t>
         </is>
       </c>
       <c r="C5" s="34" t="inlineStr">
         <is>
-          <t>fsa:RaisingOfDebtToAssociates</t>
-        </is>
-      </c>
-      <c r="D5" s="35" t="n">
-        <v>-22495</v>
-      </c>
-      <c r="E5" s="35" t="n">
-        <v>0</v>
-      </c>
+          <t>fsa:RefundInJointAssessment</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="n"/>
+      <c r="E5" s="35" t="n"/>
       <c r="F5" s="35" t="n"/>
       <c r="G5" s="35" t="n"/>
-      <c r="H5" s="35" t="n"/>
+      <c r="H5" s="35" t="n">
+        <v>14727</v>
+      </c>
       <c r="I5" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7646,12 +7642,12 @@
       </c>
       <c r="B6" s="37" t="inlineStr">
         <is>
-          <t>fsa:RefundInJointAssessment</t>
+          <t>fsa:ResearchAndDevelopmentExpenditure</t>
         </is>
       </c>
       <c r="C6" s="37" t="inlineStr">
         <is>
-          <t>fsa:RefundInJointAssessment</t>
+          <t>fsa:ResearchAndDevelopmentExpenditure</t>
         </is>
       </c>
       <c r="D6" s="38" t="n"/>
@@ -7659,7 +7655,7 @@
       <c r="F6" s="38" t="n"/>
       <c r="G6" s="38" t="n"/>
       <c r="H6" s="38" t="n">
-        <v>14727</v>
+        <v>149211</v>
       </c>
       <c r="I6" s="39" t="inlineStr">
         <is>
@@ -7675,21 +7671,27 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>fsa:ResearchAndDevelopmentExpenditure</t>
+          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
         </is>
       </c>
       <c r="C7" s="34" t="inlineStr">
         <is>
-          <t>fsa:ResearchAndDevelopmentExpenditure</t>
-        </is>
-      </c>
-      <c r="D7" s="35" t="n"/>
-      <c r="E7" s="35" t="n"/>
-      <c r="F7" s="35" t="n"/>
-      <c r="G7" s="35" t="n"/>
-      <c r="H7" s="35" t="n">
-        <v>149211</v>
-      </c>
+          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="n">
+        <v>-3613</v>
+      </c>
+      <c r="E7" s="35" t="n">
+        <v>3209</v>
+      </c>
+      <c r="F7" s="35" t="n">
+        <v>9525</v>
+      </c>
+      <c r="G7" s="35" t="n">
+        <v>8289</v>
+      </c>
+      <c r="H7" s="35" t="n"/>
       <c r="I7" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7704,90 +7706,24 @@
       </c>
       <c r="B8" s="37" t="inlineStr">
         <is>
-          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
+          <t>fsa:TransferredToFromOtherStatutoryReserves</t>
         </is>
       </c>
       <c r="C8" s="37" t="inlineStr">
         <is>
-          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
-        </is>
-      </c>
-      <c r="D8" s="38" t="n">
-        <v>-3613</v>
-      </c>
-      <c r="E8" s="38" t="n">
-        <v>3209</v>
-      </c>
-      <c r="F8" s="38" t="n">
-        <v>9525</v>
-      </c>
+          <t>fsa:TransferredToFromOtherStatutoryReserves</t>
+        </is>
+      </c>
+      <c r="D8" s="38" t="n"/>
+      <c r="E8" s="38" t="n"/>
+      <c r="F8" s="38" t="n"/>
       <c r="G8" s="38" t="n">
-        <v>8289</v>
-      </c>
-      <c r="H8" s="38" t="n"/>
+        <v>50269</v>
+      </c>
+      <c r="H8" s="38" t="n">
+        <v>33945</v>
+      </c>
       <c r="I8" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B9" s="34" t="inlineStr">
-        <is>
-          <t>fsa:TransferredToFromOtherStatutoryReserves</t>
-        </is>
-      </c>
-      <c r="C9" s="34" t="inlineStr">
-        <is>
-          <t>fsa:TransferredToFromOtherStatutoryReserves</t>
-        </is>
-      </c>
-      <c r="D9" s="35" t="n"/>
-      <c r="E9" s="35" t="n"/>
-      <c r="F9" s="35" t="n"/>
-      <c r="G9" s="35" t="n">
-        <v>50269</v>
-      </c>
-      <c r="H9" s="35" t="n">
-        <v>33945</v>
-      </c>
-      <c r="I9" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B10" s="37" t="inlineStr">
-        <is>
-          <t>fsa:WritedownsOfCurrentAssets</t>
-        </is>
-      </c>
-      <c r="C10" s="37" t="inlineStr">
-        <is>
-          <t>fsa:WritedownsOfCurrentAssets</t>
-        </is>
-      </c>
-      <c r="D10" s="38" t="n">
-        <v>-4075</v>
-      </c>
-      <c r="E10" s="38" t="n">
-        <v>-4994</v>
-      </c>
-      <c r="F10" s="38" t="n"/>
-      <c r="G10" s="38" t="n"/>
-      <c r="H10" s="38" t="n"/>
-      <c r="I10" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>

--- a/filer/25834844_fertin.xlsx
+++ b/filer/25834844_fertin.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/25834844_fertin.xlsx
+++ b/filer/25834844_fertin.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik_25834844" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw_25834844" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw_25834844" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_funktion" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw_25834844" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_funktion" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -204,9 +205,9 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -628,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -662,7 +663,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -677,35 +678,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1435,35 +1436,35 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
@@ -2913,35 +2914,35 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K52" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
@@ -4295,19 +4296,19 @@
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1">
@@ -4413,19 +4414,19 @@
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C86" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1">
@@ -4722,6 +4723,148 @@
       </c>
       <c r="F97" s="13">
         <f>IFERROR($F$34/($F$59+$F$66)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.kr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B100" s="17">
+        <f>'pengestrom_raw_25834844'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C100" s="17">
+        <f>'pengestrom_raw_25834844'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D100" s="17">
+        <f>'pengestrom_raw_25834844'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E100" s="17">
+        <f>'pengestrom_raw_25834844'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F100" s="17">
+        <f>'pengestrom_raw_25834844'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B101" s="17">
+        <f>'pengestrom_raw_25834844'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C101" s="17">
+        <f>'pengestrom_raw_25834844'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D101" s="17">
+        <f>'pengestrom_raw_25834844'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E101" s="17">
+        <f>'pengestrom_raw_25834844'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F101" s="17">
+        <f>'pengestrom_raw_25834844'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B102" s="17">
+        <f>'pengestrom_raw_25834844'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C102" s="17">
+        <f>'pengestrom_raw_25834844'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D102" s="17">
+        <f>'pengestrom_raw_25834844'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E102" s="17">
+        <f>'pengestrom_raw_25834844'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F102" s="17">
+        <f>'pengestrom_raw_25834844'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B103" s="17">
+        <f>'pengestrom_raw_25834844'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C103" s="17">
+        <f>'pengestrom_raw_25834844'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D103" s="17">
+        <f>'pengestrom_raw_25834844'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E103" s="17">
+        <f>'pengestrom_raw_25834844'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F103" s="17">
+        <f>'pengestrom_raw_25834844'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B104">
+        <f>IF(ABS(('pengestrom_raw_25834844'!$B$2+'pengestrom_raw_25834844'!$B$3+'pengestrom_raw_25834844'!$B$4)-'pengestrom_raw_25834844'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_25834844'!$B$2+'pengestrom_raw_25834844'!$B$3+'pengestrom_raw_25834844'!$B$4)-'pengestrom_raw_25834844'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C104">
+        <f>IF(ABS(('pengestrom_raw_25834844'!$C$2+'pengestrom_raw_25834844'!$C$3+'pengestrom_raw_25834844'!$C$4)-'pengestrom_raw_25834844'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_25834844'!$C$2+'pengestrom_raw_25834844'!$C$3+'pengestrom_raw_25834844'!$C$4)-'pengestrom_raw_25834844'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D104">
+        <f>IF(ABS(('pengestrom_raw_25834844'!$D$2+'pengestrom_raw_25834844'!$D$3+'pengestrom_raw_25834844'!$D$4)-'pengestrom_raw_25834844'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_25834844'!$D$2+'pengestrom_raw_25834844'!$D$3+'pengestrom_raw_25834844'!$D$4)-'pengestrom_raw_25834844'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E104">
+        <f>IF(ABS(('pengestrom_raw_25834844'!$E$2+'pengestrom_raw_25834844'!$E$3+'pengestrom_raw_25834844'!$E$4)-'pengestrom_raw_25834844'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_25834844'!$E$2+'pengestrom_raw_25834844'!$E$3+'pengestrom_raw_25834844'!$E$4)-'pengestrom_raw_25834844'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F104">
+        <f>IF(ABS(('pengestrom_raw_25834844'!$F$2+'pengestrom_raw_25834844'!$F$3+'pengestrom_raw_25834844'!$F$4)-'pengestrom_raw_25834844'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_25834844'!$F$2+'pengestrom_raw_25834844'!$F$3+'pengestrom_raw_25834844'!$F$4)-'pengestrom_raw_25834844'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4754,381 +4897,371 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>991107</v>
-      </c>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>932545</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>892580</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>1012566</v>
       </c>
-      <c r="F2" s="16" t="n">
-        <v>1104175</v>
+      <c r="E2" s="17" t="n">
+        <v>1393874</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>1676276</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Produktionsomkostninger</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
-        <v>744713</v>
-      </c>
-      <c r="C3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>771161</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>867416</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>978422</v>
       </c>
-      <c r="F3" s="16" t="n">
-        <v>1004228</v>
-      </c>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>246394</v>
-      </c>
-      <c r="C4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>161384</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>25164</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>34144</v>
       </c>
-      <c r="F4" s="16" t="n">
-        <v>99947</v>
+      <c r="E4" s="17" t="n">
+        <v>691538</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>755278</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Salgs- og distributionsomkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>21724</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>19854</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>39516</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>43450</v>
       </c>
-      <c r="F5" s="16" t="n">
-        <v>41686</v>
-      </c>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Administrationsomkostninger</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>32852</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>45182</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>60457</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>66597</v>
       </c>
-      <c r="F6" s="16" t="n">
-        <v>75017</v>
-      </c>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>40200</v>
-      </c>
-      <c r="C7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n">
-        <v>15</v>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n">
+        <v>1748</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>2098</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="16" t="n">
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n">
         <v>44</v>
       </c>
+      <c r="F8" s="17" t="n">
+        <v>6717</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>232018</v>
-      </c>
-      <c r="C9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>96348</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>-74809</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>-75903</v>
       </c>
-      <c r="F9" s="16" t="n">
-        <v>-165996</v>
+      <c r="E9" s="17" t="n">
+        <v>-312963</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>-269178</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
-        <v>-7646</v>
-      </c>
-      <c r="C10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>-13069</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>-24831</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>-37072</v>
       </c>
-      <c r="F10" s="16" t="n">
-        <v>-84018</v>
+      <c r="E10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>758</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>1144</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>134</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>3998</v>
       </c>
-      <c r="F11" s="16" t="n">
-        <v>16375</v>
+      <c r="E11" s="17" t="n">
+        <v>1626</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>2438</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
-        <v>26667</v>
-      </c>
-      <c r="C12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>29513</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>14083</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>53997</v>
       </c>
-      <c r="F12" s="16" t="n">
-        <v>74042</v>
+      <c r="E12" s="17" t="n">
+        <v>130903</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>89498</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
-        <v>-26000</v>
-      </c>
-      <c r="C13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>-28000</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>-39000</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>-87000</v>
       </c>
-      <c r="F13" s="16" t="n">
-        <v>-142000</v>
+      <c r="E13" s="17" t="n">
+        <v>-129000</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>-87000</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
-        <v>198463</v>
-      </c>
-      <c r="C14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>54910</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>-113589</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>-162974</v>
       </c>
-      <c r="F14" s="16" t="n">
-        <v>-307681</v>
+      <c r="E14" s="17" t="n">
+        <v>-442240</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>-356238</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
-        <v>43052</v>
-      </c>
-      <c r="C15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>17268</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>-22213</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>-26273</v>
       </c>
-      <c r="F15" s="16" t="n">
-        <v>-48670</v>
+      <c r="E15" s="17" t="n">
+        <v>-71768</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>-74797</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
-        <v>155411</v>
-      </c>
-      <c r="C16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>37642</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>-91376</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>-136701</v>
       </c>
-      <c r="F16" s="16" t="n">
-        <v>-259011</v>
+      <c r="E16" s="17" t="n">
+        <v>-370472</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>-280841</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
-        <v>622</v>
-      </c>
-      <c r="C17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>654</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>690</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>798</v>
       </c>
-      <c r="F17" s="16" t="n">
-        <v>868</v>
+      <c r="E17" s="17" t="n">
+        <v>1182</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>1233</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>-61000</v>
-      </c>
-      <c r="C18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>-123000</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>-158000</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>123000</v>
       </c>
-      <c r="F18" s="16" t="n">
-        <v>101000</v>
+      <c r="E18" s="17" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>221000</v>
       </c>
     </row>
   </sheetData>
@@ -5160,1109 +5293,1115 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Udviklingsprojekter</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>74169</v>
-      </c>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>138100</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>149497</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>166428</v>
       </c>
-      <c r="F2" s="16" t="n">
-        <v>172678</v>
+      <c r="E2" s="17" t="n">
+        <v>435254</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>364205</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Patenter, varemærker mv.</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n"/>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n">
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n">
         <v>73894</v>
       </c>
-      <c r="F4" s="16" t="n">
-        <v>154664</v>
+      <c r="E4" s="17" t="n">
+        <v>430023</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>394894</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>354281</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>372548</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>421824</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>481249</v>
       </c>
-      <c r="F5" s="16" t="n">
-        <v>606130</v>
+      <c r="E5" s="17" t="n">
+        <v>1309266</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>1190276</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Grunde og bygninger</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>522537</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>496262</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>486193</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>456633</v>
       </c>
-      <c r="F6" s="16" t="n">
-        <v>452872</v>
+      <c r="E6" s="17" t="n">
+        <v>607570</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>577924</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Produktionsanlæg og maskiner</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>497943</v>
-      </c>
-      <c r="C7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>485156</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>445169</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>418644</v>
       </c>
-      <c r="F7" s="16" t="n">
-        <v>454139</v>
+      <c r="E7" s="17" t="n">
+        <v>593750</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>639805</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Driftsmateriel og inventar</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
-        <v>8782</v>
-      </c>
-      <c r="C8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>6709</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>4680</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>4438</v>
       </c>
-      <c r="F8" s="16" t="n">
-        <v>7872</v>
+      <c r="E8" s="17" t="n">
+        <v>17153</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>10507</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Indretning af lejede lokaler</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>414</v>
-      </c>
-      <c r="C9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>287</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>159</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>32</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="E9" s="17" t="n">
+        <v>8392</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>35061</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Forudbetaling og anlægsaktiver under opførelse</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n">
+        <v>136164</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>240272</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>313499</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>239112</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>269644</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Materielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n">
+        <v>1124578</v>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>1176473</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>1193246</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>1465977</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>1532941</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Kapitalandele, dattervirksomheder</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n">
+        <v>79711</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>65747</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>67663</v>
+      </c>
+      <c r="E12" s="17" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>Forudbetaling og anlægsaktiver under opførelse</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="n">
-        <v>69146</v>
-      </c>
-      <c r="C10" s="16" t="n">
-        <v>136164</v>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>240272</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>313499</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>172246</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>Materielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="n">
-        <v>1098822</v>
-      </c>
-      <c r="C11" s="16" t="n">
-        <v>1124578</v>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>1176473</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>1193246</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>1087129</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>Kapitalandele, dattervirksomheder</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="n">
-        <v>81818</v>
-      </c>
-      <c r="C12" s="16" t="n">
+      <c r="F12" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>Deposita</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Finansielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
         <v>79711</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>65747</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>67663</v>
       </c>
-      <c r="F12" s="16" t="n">
-        <v>119458</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>Deposita</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>Finansielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n">
-        <v>81818</v>
-      </c>
-      <c r="C14" s="16" t="n">
-        <v>79711</v>
-      </c>
-      <c r="D14" s="16" t="n">
-        <v>65747</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>67663</v>
-      </c>
-      <c r="F14" s="16" t="n">
-        <v>119458</v>
+      <c r="E14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
-        <v>1534921</v>
-      </c>
-      <c r="C15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>1576837</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>1664044</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>1742158</v>
       </c>
-      <c r="F15" s="16" t="n">
-        <v>1812717</v>
+      <c r="E15" s="17" t="n">
+        <v>2775243</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>2723217</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Råvarer og hjælpematerialer</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
-        <v>77256</v>
-      </c>
-      <c r="C16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>124065</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>144678</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>145576</v>
       </c>
-      <c r="F16" s="16" t="n">
-        <v>124160</v>
+      <c r="E16" s="17" t="n">
+        <v>164064</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>207993</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Varer under fremstilling</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
-        <v>26809</v>
-      </c>
-      <c r="C17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>13392</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>30001</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>31358</v>
       </c>
-      <c r="F17" s="16" t="n">
-        <v>27572</v>
+      <c r="E17" s="17" t="n">
+        <v>40534</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>48879</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Færdigvarer og handelsvarer</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>56575</v>
-      </c>
-      <c r="C18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>61293</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>43917</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>96315</v>
       </c>
-      <c r="F18" s="16" t="n">
-        <v>101504</v>
+      <c r="E18" s="17" t="n">
+        <v>113719</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>108360</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
-        <v>160640</v>
-      </c>
-      <c r="C19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>198750</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>218596</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>273249</v>
       </c>
-      <c r="F19" s="16" t="n">
-        <v>253236</v>
+      <c r="E19" s="17" t="n">
+        <v>318317</v>
+      </c>
+      <c r="F19" s="17" t="n">
+        <v>365232</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
-        <v>208029</v>
-      </c>
-      <c r="C20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>146069</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="C20" s="17" t="n">
         <v>156794</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <v>149426</v>
       </c>
-      <c r="F20" s="16" t="n">
-        <v>139857</v>
+      <c r="E20" s="17" t="n">
+        <v>222076</v>
+      </c>
+      <c r="F20" s="17" t="n">
+        <v>295663</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
-        <v>18432</v>
-      </c>
-      <c r="C21" s="16" t="n">
+      <c r="B21" s="17" t="n">
         <v>55830</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="C21" s="17" t="n">
         <v>177215</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="D21" s="17" t="n">
         <v>315001</v>
       </c>
-      <c r="F21" s="16" t="n">
-        <v>338362</v>
+      <c r="E21" s="17" t="n">
+        <v>26552</v>
+      </c>
+      <c r="F21" s="17" t="n">
+        <v>30596</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Andre tilgodehavender</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
-        <v>10351</v>
-      </c>
-      <c r="C22" s="16" t="n">
+      <c r="B22" s="17" t="n">
         <v>4284</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="C22" s="17" t="n">
         <v>355</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="D22" s="17" t="n">
         <v>1755</v>
       </c>
-      <c r="F22" s="16" t="n">
-        <v>8894</v>
+      <c r="E22" s="17" t="n">
+        <v>49554</v>
+      </c>
+      <c r="F22" s="17" t="n">
+        <v>50669</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
-        <v>3034</v>
-      </c>
-      <c r="C23" s="16" t="n">
+      <c r="B23" s="17" t="n">
         <v>3291</v>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="C23" s="17" t="n">
         <v>6072</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="D23" s="17" t="n">
         <v>10198</v>
       </c>
-      <c r="F23" s="16" t="n">
-        <v>9655</v>
+      <c r="E23" s="17" t="n">
+        <v>17048</v>
+      </c>
+      <c r="F23" s="17" t="n">
+        <v>18852</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="16" t="n"/>
-      <c r="D24" s="16" t="n"/>
-      <c r="E24" s="16" t="n"/>
-      <c r="F24" s="16" t="n"/>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="16" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="16" t="n"/>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="17" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
-        <v>239846</v>
-      </c>
-      <c r="C27" s="16" t="n">
+      <c r="B27" s="17" t="n">
         <v>209474</v>
       </c>
-      <c r="D27" s="16" t="n">
+      <c r="C27" s="17" t="n">
         <v>340436</v>
       </c>
-      <c r="E27" s="16" t="n">
+      <c r="D27" s="17" t="n">
         <v>476970</v>
       </c>
-      <c r="F27" s="16" t="n">
-        <v>496768</v>
+      <c r="E27" s="17" t="n">
+        <v>315230</v>
+      </c>
+      <c r="F27" s="17" t="n">
+        <v>395780</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Værdipapirer</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Likvide beholdninger</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n">
-        <v>62977</v>
-      </c>
-      <c r="C29" s="16" t="n">
+      <c r="B29" s="17" t="n">
         <v>36428</v>
       </c>
-      <c r="D29" s="16" t="n">
+      <c r="C29" s="17" t="n">
         <v>26399</v>
       </c>
-      <c r="E29" s="16" t="n">
+      <c r="D29" s="17" t="n">
         <v>5822</v>
       </c>
-      <c r="F29" s="16" t="n">
-        <v>8064</v>
+      <c r="E29" s="17" t="n">
+        <v>60318</v>
+      </c>
+      <c r="F29" s="17" t="n">
+        <v>122828</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n">
-        <v>463463</v>
-      </c>
-      <c r="C30" s="16" t="n">
+      <c r="B30" s="17" t="n">
         <v>444652</v>
       </c>
-      <c r="D30" s="16" t="n">
+      <c r="C30" s="17" t="n">
         <v>585431</v>
       </c>
-      <c r="E30" s="16" t="n">
+      <c r="D30" s="17" t="n">
         <v>756041</v>
       </c>
-      <c r="F30" s="16" t="n">
-        <v>758068</v>
+      <c r="E30" s="17" t="n">
+        <v>693865</v>
+      </c>
+      <c r="F30" s="17" t="n">
+        <v>883840</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>Aktiver</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n">
-        <v>1998384</v>
-      </c>
-      <c r="C31" s="16" t="n">
+      <c r="B31" s="17" t="n">
         <v>2021489</v>
       </c>
-      <c r="D31" s="16" t="n">
+      <c r="C31" s="17" t="n">
         <v>2249475</v>
       </c>
-      <c r="E31" s="16" t="n">
+      <c r="D31" s="17" t="n">
         <v>2498199</v>
       </c>
-      <c r="F31" s="16" t="n">
-        <v>2570785</v>
+      <c r="E31" s="17" t="n">
+        <v>3469108</v>
+      </c>
+      <c r="F31" s="17" t="n">
+        <v>3607057</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Selskabskapital</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n">
+      <c r="B32" s="17" t="n">
         <v>70510</v>
       </c>
-      <c r="C32" s="16" t="n">
-        <v>70510</v>
-      </c>
-      <c r="D32" s="16" t="n">
+      <c r="C32" s="17" t="n">
         <v>70511</v>
       </c>
-      <c r="E32" s="16" t="n">
+      <c r="D32" s="17" t="n">
         <v>70511</v>
       </c>
-      <c r="F32" s="16" t="n">
+      <c r="E32" s="17" t="n">
         <v>1370511</v>
       </c>
+      <c r="F32" s="17" t="n">
+        <v>1370511</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n"/>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="16" t="n"/>
-      <c r="E33" s="16" t="n"/>
-      <c r="F33" s="16" t="n"/>
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="17" t="n"/>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="17" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n">
-        <v>206148</v>
-      </c>
-      <c r="C34" s="16" t="n">
+      <c r="B34" s="17" t="n">
         <v>234984</v>
       </c>
-      <c r="D34" s="16" t="n">
+      <c r="C34" s="17" t="n">
         <v>267929</v>
       </c>
-      <c r="E34" s="16" t="n">
+      <c r="D34" s="17" t="n">
         <v>318198</v>
       </c>
-      <c r="F34" s="16" t="n">
-        <v>352143</v>
+      <c r="E34" s="17" t="n">
+        <v>549163</v>
+      </c>
+      <c r="F34" s="17" t="n">
+        <v>462871</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="17" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Andre reserver</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n"/>
-      <c r="C36" s="16" t="n"/>
-      <c r="D36" s="16" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="16" t="n"/>
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="17" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Overført resultat</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n">
-        <v>367081</v>
-      </c>
-      <c r="C37" s="16" t="n">
+      <c r="B37" s="17" t="n">
         <v>372701</v>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="C37" s="17" t="n">
         <v>248380</v>
       </c>
-      <c r="E37" s="16" t="n">
+      <c r="D37" s="17" t="n">
         <v>61410</v>
       </c>
-      <c r="F37" s="16" t="n">
-        <v>-219104</v>
+      <c r="E37" s="17" t="n">
+        <v>-354287</v>
+      </c>
+      <c r="F37" s="17" t="n">
+        <v>-563482</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>Egenkapital i alt</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n">
-        <v>770126</v>
-      </c>
-      <c r="C38" s="16" t="n">
+      <c r="B38" s="17" t="n">
         <v>681404</v>
       </c>
-      <c r="D38" s="16" t="n">
+      <c r="C38" s="17" t="n">
         <v>596345</v>
       </c>
-      <c r="E38" s="16" t="n">
+      <c r="D38" s="17" t="n">
         <v>458408</v>
       </c>
-      <c r="F38" s="16" t="n">
-        <v>1503550</v>
+      <c r="E38" s="17" t="n">
+        <v>1565387</v>
+      </c>
+      <c r="F38" s="17" t="n">
+        <v>1269900</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Hensættelse til udskudt skat</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n">
-        <v>150464</v>
-      </c>
-      <c r="C39" s="16" t="n">
+      <c r="B39" s="17" t="n">
         <v>160726</v>
       </c>
-      <c r="D39" s="16" t="n">
+      <c r="C39" s="17" t="n">
         <v>139981</v>
       </c>
-      <c r="E39" s="16" t="n">
+      <c r="D39" s="17" t="n">
         <v>125775</v>
       </c>
-      <c r="F39" s="16" t="n">
-        <v>91832</v>
+      <c r="E39" s="17" t="n">
+        <v>151037</v>
+      </c>
+      <c r="F39" s="17" t="n">
+        <v>85166</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>Hensatte forpligtelser</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n">
-        <v>150464</v>
-      </c>
-      <c r="C40" s="16" t="n">
+      <c r="B40" s="17" t="n">
         <v>160726</v>
       </c>
-      <c r="D40" s="16" t="n">
+      <c r="C40" s="17" t="n">
         <v>139981</v>
       </c>
-      <c r="E40" s="16" t="n">
+      <c r="D40" s="17" t="n">
         <v>125775</v>
       </c>
-      <c r="F40" s="16" t="n">
-        <v>91832</v>
+      <c r="E40" s="17" t="n">
+        <v>151037</v>
+      </c>
+      <c r="F40" s="17" t="n">
+        <v>85166</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (langfristet)</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="17" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>Langfristede lån</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n">
-        <v>588521</v>
-      </c>
-      <c r="C42" s="16" t="n">
+      <c r="B42" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
+      <c r="C42" s="17" t="n"/>
+      <c r="D42" s="17" t="n"/>
+      <c r="E42" s="17" t="n"/>
+      <c r="F42" s="17" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="16" t="n"/>
-      <c r="D43" s="16" t="n"/>
-      <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n"/>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="17" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (langfristet)</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n">
-        <v>36135</v>
-      </c>
-      <c r="C44" s="16" t="n">
+      <c r="B44" s="17" t="n">
         <v>37195</v>
       </c>
-      <c r="D44" s="16" t="n">
+      <c r="C44" s="17" t="n">
         <v>36898</v>
       </c>
-      <c r="E44" s="16" t="n">
+      <c r="D44" s="17" t="n">
         <v>1564541</v>
       </c>
-      <c r="F44" s="16" t="n">
-        <v>633642</v>
+      <c r="E44" s="17" t="n">
+        <v>1272422</v>
+      </c>
+      <c r="F44" s="17" t="n">
+        <v>1600000</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="inlineStr">
+      <c r="A45" s="15" t="inlineStr">
         <is>
           <t>Langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n">
-        <v>624656</v>
-      </c>
-      <c r="C45" s="16" t="n">
+      <c r="B45" s="17" t="n">
         <v>37195</v>
       </c>
-      <c r="D45" s="16" t="n">
+      <c r="C45" s="17" t="n">
         <v>36898</v>
       </c>
-      <c r="E45" s="16" t="n">
+      <c r="D45" s="17" t="n">
         <v>1602229</v>
       </c>
-      <c r="F45" s="16" t="n">
-        <v>689799</v>
+      <c r="E45" s="17" t="n">
+        <v>1328579</v>
+      </c>
+      <c r="F45" s="17" t="n">
+        <v>1654366</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="16" t="n"/>
-      <c r="D46" s="16" t="n"/>
-      <c r="E46" s="16" t="n"/>
-      <c r="F46" s="16" t="n"/>
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="17" t="n"/>
+      <c r="F46" s="17" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n"/>
-      <c r="C47" s="16" t="n"/>
-      <c r="D47" s="16" t="n">
+      <c r="B47" s="17" t="n"/>
+      <c r="C47" s="17" t="n">
         <v>439</v>
       </c>
-      <c r="E47" s="16" t="n">
+      <c r="D47" s="17" t="n">
         <v>698</v>
       </c>
-      <c r="F47" s="16" t="n">
+      <c r="E47" s="17" t="n">
         <v>556</v>
       </c>
+      <c r="F47" s="17" t="n">
+        <v>23098</v>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>Kreditinstitutter</t>
         </is>
       </c>
-      <c r="B48" s="16" t="n">
+      <c r="B48" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C48" s="16" t="n">
+      <c r="C48" s="17" t="n"/>
+      <c r="D48" s="17" t="n"/>
+      <c r="E48" s="17" t="n"/>
+      <c r="F48" s="17" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>Leasingforpligtelser (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="n"/>
+      <c r="C49" s="17" t="n"/>
+      <c r="D49" s="17" t="n"/>
+      <c r="E49" s="17" t="n"/>
+      <c r="F49" s="17" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>Leverandører af varer og tjenesteydelser</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="n">
+        <v>97042</v>
+      </c>
+      <c r="C50" s="17" t="n">
+        <v>84883</v>
+      </c>
+      <c r="D50" s="17" t="n">
+        <v>101687</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>134031</v>
+      </c>
+      <c r="F50" s="17" t="n">
+        <v>233520</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>Gæld til tilknyttede virksomheder</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="n">
+        <v>950661</v>
+      </c>
+      <c r="C51" s="17" t="n">
+        <v>1237235</v>
+      </c>
+      <c r="D51" s="17" t="n">
+        <v>36248</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>58183</v>
+      </c>
+      <c r="F51" s="17" t="n">
+        <v>168397</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="n"/>
+      <c r="C52" s="17" t="n"/>
+      <c r="D52" s="17" t="n"/>
+      <c r="E52" s="17" t="n"/>
+      <c r="F52" s="17" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>Selskabsskat</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="n"/>
+      <c r="C53" s="17" t="n"/>
+      <c r="D53" s="17" t="n"/>
+      <c r="E53" s="17" t="n"/>
+      <c r="F53" s="17" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="n">
+        <v>7006</v>
+      </c>
+      <c r="C54" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D48" s="16" t="n"/>
-      <c r="E48" s="16" t="n"/>
-      <c r="F48" s="16" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="15" t="inlineStr">
-        <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B49" s="16" t="n"/>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="16" t="n"/>
-      <c r="E49" s="16" t="n"/>
-      <c r="F49" s="16" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="15" t="inlineStr">
-        <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
-        </is>
-      </c>
-      <c r="B50" s="16" t="n">
-        <v>61653</v>
-      </c>
-      <c r="C50" s="16" t="n">
-        <v>97042</v>
-      </c>
-      <c r="D50" s="16" t="n">
-        <v>84883</v>
-      </c>
-      <c r="E50" s="16" t="n">
-        <v>101687</v>
-      </c>
-      <c r="F50" s="16" t="n">
-        <v>108850</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="15" t="inlineStr">
-        <is>
-          <t>Gæld til tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B51" s="16" t="n">
-        <v>84224</v>
-      </c>
-      <c r="C51" s="16" t="n">
-        <v>950661</v>
-      </c>
-      <c r="D51" s="16" t="n">
-        <v>1237235</v>
-      </c>
-      <c r="E51" s="16" t="n">
-        <v>36248</v>
-      </c>
-      <c r="F51" s="16" t="n">
-        <v>3329</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="15" t="inlineStr">
-        <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
-        </is>
-      </c>
-      <c r="B52" s="16" t="n"/>
-      <c r="C52" s="16" t="n"/>
-      <c r="D52" s="16" t="n"/>
-      <c r="E52" s="16" t="n"/>
-      <c r="F52" s="16" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="15" t="inlineStr">
-        <is>
-          <t>Selskabsskat</t>
-        </is>
-      </c>
-      <c r="B53" s="16" t="n"/>
-      <c r="C53" s="16" t="n"/>
-      <c r="D53" s="16" t="n"/>
-      <c r="E53" s="16" t="n"/>
-      <c r="F53" s="16" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="15" t="inlineStr">
-        <is>
-          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
-        </is>
-      </c>
-      <c r="B54" s="16" t="n">
-        <v>6127</v>
-      </c>
-      <c r="C54" s="16" t="n">
-        <v>7006</v>
-      </c>
-      <c r="D54" s="16" t="n">
+      <c r="D54" s="17" t="n"/>
+      <c r="E54" s="17" t="n">
+        <v>6483</v>
+      </c>
+      <c r="F54" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E54" s="16" t="n"/>
-      <c r="F54" s="16" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="15" t="inlineStr">
+      <c r="A55" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
-      <c r="B55" s="16" t="n">
-        <v>101134</v>
-      </c>
-      <c r="C55" s="16" t="n">
+      <c r="B55" s="17" t="n">
         <v>87455</v>
       </c>
-      <c r="D55" s="16" t="n">
+      <c r="C55" s="17" t="n">
         <v>153694</v>
       </c>
-      <c r="E55" s="16" t="n">
+      <c r="D55" s="17" t="n">
         <v>173154</v>
       </c>
-      <c r="F55" s="16" t="n">
-        <v>172869</v>
+      <c r="E55" s="17" t="n">
+        <v>205509</v>
+      </c>
+      <c r="F55" s="17" t="n">
+        <v>149465</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="15" t="inlineStr">
+      <c r="A56" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
-      <c r="B56" s="16" t="n"/>
-      <c r="C56" s="16" t="n"/>
-      <c r="D56" s="16" t="n"/>
-      <c r="E56" s="16" t="n"/>
-      <c r="F56" s="16" t="n"/>
+      <c r="B56" s="17" t="n"/>
+      <c r="C56" s="17" t="n"/>
+      <c r="D56" s="17" t="n"/>
+      <c r="E56" s="17" t="n">
+        <v>19343</v>
+      </c>
+      <c r="F56" s="17" t="n">
+        <v>23145</v>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="17" t="inlineStr">
+      <c r="A57" s="15" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B57" s="16" t="n">
-        <v>453138</v>
-      </c>
-      <c r="C57" s="16" t="n">
+      <c r="B57" s="17" t="n">
         <v>1142164</v>
       </c>
-      <c r="D57" s="16" t="n">
+      <c r="C57" s="17" t="n">
         <v>1476251</v>
       </c>
-      <c r="E57" s="16" t="n">
+      <c r="D57" s="17" t="n">
         <v>311787</v>
       </c>
-      <c r="F57" s="16" t="n">
-        <v>285604</v>
+      <c r="E57" s="17" t="n">
+        <v>424105</v>
+      </c>
+      <c r="F57" s="17" t="n">
+        <v>597625</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="17" t="inlineStr">
+      <c r="A58" s="15" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B58" s="16" t="n">
-        <v>1077794</v>
-      </c>
-      <c r="C58" s="16" t="n">
+      <c r="B58" s="17" t="n">
         <v>1179359</v>
       </c>
-      <c r="D58" s="16" t="n">
+      <c r="C58" s="17" t="n">
         <v>1513149</v>
       </c>
-      <c r="E58" s="16" t="n">
+      <c r="D58" s="17" t="n">
         <v>1914016</v>
       </c>
-      <c r="F58" s="16" t="n">
-        <v>975403</v>
+      <c r="E58" s="17" t="n">
+        <v>1752684</v>
+      </c>
+      <c r="F58" s="17" t="n">
+        <v>2251991</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="17" t="inlineStr">
+      <c r="A59" s="15" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B59" s="16" t="n">
-        <v>1998384</v>
-      </c>
-      <c r="C59" s="16" t="n">
+      <c r="B59" s="17" t="n">
         <v>2021489</v>
       </c>
-      <c r="D59" s="16" t="n">
+      <c r="C59" s="17" t="n">
         <v>2249475</v>
       </c>
-      <c r="E59" s="16" t="n">
+      <c r="D59" s="17" t="n">
         <v>2498199</v>
       </c>
-      <c r="F59" s="16" t="n">
-        <v>2570785</v>
+      <c r="E59" s="17" t="n">
+        <v>3469108</v>
+      </c>
+      <c r="F59" s="17" t="n">
+        <v>3607057</v>
       </c>
     </row>
   </sheetData>
@@ -6271,6 +6410,116 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.kr.)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>175241</v>
+      </c>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n">
+        <v>-110588</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>-75363</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>-201056</v>
+      </c>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n">
+        <v>-377168</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>-294339</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>-734</v>
+      </c>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n">
+        <v>518814</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>432212</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6301,13 +6550,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -6997,7 +7246,7 @@
     <row r="39">
       <c r="A39" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B39" s="22" t="n"/>
@@ -7115,7 +7364,7 @@
     <row r="46">
       <c r="A46" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B46" s="22" t="n"/>
@@ -7291,7 +7540,7 @@
     <row r="57">
       <c r="A57" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B57" s="29" t="n"/>
@@ -7469,13 +7718,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7514,27 +7763,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2020 t.kr.</t>
+          <t>2021 t.kr.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2021 t.kr.</t>
+          <t>2022 t.kr.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2022 t.kr.</t>
+          <t>2023 t.kr.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2023 t.kr.</t>
+          <t>2024 t.kr.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2024 t.kr.</t>
+          <t>2025 t.kr.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -7560,11 +7809,9 @@
         </is>
       </c>
       <c r="D3" s="35" t="n">
-        <v>36925</v>
-      </c>
-      <c r="E3" s="35" t="n">
         <v>10262</v>
       </c>
+      <c r="E3" s="35" t="n"/>
       <c r="F3" s="35" t="n"/>
       <c r="G3" s="35" t="n"/>
       <c r="H3" s="35" t="n"/>
@@ -7582,23 +7829,23 @@
       </c>
       <c r="B4" s="37" t="inlineStr">
         <is>
-          <t>fsa:RaisingOfDebtToAssociates</t>
+          <t>fsa:AdjustmentsOfOtherTaxExpenses</t>
         </is>
       </c>
       <c r="C4" s="37" t="inlineStr">
         <is>
-          <t>fsa:RaisingOfDebtToAssociates</t>
-        </is>
-      </c>
-      <c r="D4" s="38" t="n">
-        <v>-22495</v>
-      </c>
-      <c r="E4" s="38" t="n">
-        <v>0</v>
-      </c>
+          <t>fsa:AdjustmentsOfOtherTaxExpenses</t>
+        </is>
+      </c>
+      <c r="D4" s="38" t="n"/>
+      <c r="E4" s="38" t="n"/>
       <c r="F4" s="38" t="n"/>
-      <c r="G4" s="38" t="n"/>
-      <c r="H4" s="38" t="n"/>
+      <c r="G4" s="38" t="n">
+        <v>19788</v>
+      </c>
+      <c r="H4" s="38" t="n">
+        <v>33496</v>
+      </c>
       <c r="I4" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7613,20 +7860,22 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>fsa:RefundInJointAssessment</t>
+          <t>fsa:CashCapitalIncrease</t>
         </is>
       </c>
       <c r="C5" s="34" t="inlineStr">
         <is>
-          <t>fsa:RefundInJointAssessment</t>
+          <t>fsa:CashCapitalIncrease</t>
         </is>
       </c>
       <c r="D5" s="35" t="n"/>
       <c r="E5" s="35" t="n"/>
       <c r="F5" s="35" t="n"/>
-      <c r="G5" s="35" t="n"/>
+      <c r="G5" s="35" t="n">
+        <v>1404253</v>
+      </c>
       <c r="H5" s="35" t="n">
-        <v>14727</v>
+        <v>12845</v>
       </c>
       <c r="I5" s="36" t="inlineStr">
         <is>
@@ -7642,20 +7891,22 @@
       </c>
       <c r="B6" s="37" t="inlineStr">
         <is>
-          <t>fsa:ResearchAndDevelopmentExpenditure</t>
+          <t>fsa:OtherSimilarRightsOriginatingFromDevelopmentProjects</t>
         </is>
       </c>
       <c r="C6" s="37" t="inlineStr">
         <is>
-          <t>fsa:ResearchAndDevelopmentExpenditure</t>
+          <t>fsa:OtherSimilarRightsOriginatingFromDevelopmentProjects</t>
         </is>
       </c>
       <c r="D6" s="38" t="n"/>
       <c r="E6" s="38" t="n"/>
       <c r="F6" s="38" t="n"/>
-      <c r="G6" s="38" t="n"/>
+      <c r="G6" s="38" t="n">
+        <v>155804</v>
+      </c>
       <c r="H6" s="38" t="n">
-        <v>149211</v>
+        <v>148912</v>
       </c>
       <c r="I6" s="39" t="inlineStr">
         <is>
@@ -7671,27 +7922,23 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
+          <t>fsa:OtherTaxExpenses</t>
         </is>
       </c>
       <c r="C7" s="34" t="inlineStr">
         <is>
-          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
-        </is>
-      </c>
-      <c r="D7" s="35" t="n">
-        <v>-3613</v>
-      </c>
-      <c r="E7" s="35" t="n">
-        <v>3209</v>
-      </c>
-      <c r="F7" s="35" t="n">
-        <v>9525</v>
-      </c>
+          <t>fsa:OtherTaxExpenses</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="n"/>
+      <c r="E7" s="35" t="n"/>
+      <c r="F7" s="35" t="n"/>
       <c r="G7" s="35" t="n">
-        <v>8289</v>
-      </c>
-      <c r="H7" s="35" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="35" t="n">
+        <v>-600</v>
+      </c>
       <c r="I7" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7706,24 +7953,181 @@
       </c>
       <c r="B8" s="37" t="inlineStr">
         <is>
-          <t>fsa:TransferredToFromOtherStatutoryReserves</t>
+          <t>fsa:PatentsOriginatingFromDevelopmentProjects</t>
         </is>
       </c>
       <c r="C8" s="37" t="inlineStr">
         <is>
-          <t>fsa:TransferredToFromOtherStatutoryReserves</t>
+          <t>fsa:PatentsOriginatingFromDevelopmentProjects</t>
         </is>
       </c>
       <c r="D8" s="38" t="n"/>
       <c r="E8" s="38" t="n"/>
       <c r="F8" s="38" t="n"/>
       <c r="G8" s="38" t="n">
+        <v>41</v>
+      </c>
+      <c r="H8" s="38" t="n">
+        <v>29900</v>
+      </c>
+      <c r="I8" s="39" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="34" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>fsa:RaisingOfDebtToAssociates</t>
+        </is>
+      </c>
+      <c r="C9" s="34" t="inlineStr">
+        <is>
+          <t>fsa:RaisingOfDebtToAssociates</t>
+        </is>
+      </c>
+      <c r="D9" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="35" t="n"/>
+      <c r="F9" s="35" t="n"/>
+      <c r="G9" s="35" t="n"/>
+      <c r="H9" s="35" t="n"/>
+      <c r="I9" s="36" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="37" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B10" s="37" t="inlineStr">
+        <is>
+          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
+        </is>
+      </c>
+      <c r="C10" s="37" t="inlineStr">
+        <is>
+          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
+        </is>
+      </c>
+      <c r="D10" s="38" t="n">
+        <v>3209</v>
+      </c>
+      <c r="E10" s="38" t="n">
+        <v>9525</v>
+      </c>
+      <c r="F10" s="38" t="n">
+        <v>8289</v>
+      </c>
+      <c r="G10" s="38" t="n"/>
+      <c r="H10" s="38" t="n"/>
+      <c r="I10" s="39" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="34" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B11" s="34" t="inlineStr">
+        <is>
+          <t>fsa:SaleOfTreasuryShares</t>
+        </is>
+      </c>
+      <c r="C11" s="34" t="inlineStr">
+        <is>
+          <t>fsa:SaleOfTreasuryShares</t>
+        </is>
+      </c>
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="35" t="n"/>
+      <c r="F11" s="35" t="n"/>
+      <c r="G11" s="35" t="n">
+        <v>1324</v>
+      </c>
+      <c r="H11" s="35" t="n">
+        <v>34</v>
+      </c>
+      <c r="I11" s="36" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="37" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B12" s="37" t="inlineStr">
+        <is>
+          <t>fsa:TransferredToFromOtherStatutoryReserves</t>
+        </is>
+      </c>
+      <c r="C12" s="37" t="inlineStr">
+        <is>
+          <t>fsa:TransferredToFromOtherStatutoryReserves</t>
+        </is>
+      </c>
+      <c r="D12" s="38" t="n"/>
+      <c r="E12" s="38" t="n"/>
+      <c r="F12" s="38" t="n">
         <v>50269</v>
       </c>
-      <c r="H8" s="38" t="n">
-        <v>33945</v>
-      </c>
-      <c r="I8" s="39" t="inlineStr">
+      <c r="G12" s="38" t="n">
+        <v>-32353</v>
+      </c>
+      <c r="H12" s="38" t="n">
+        <v>-86292</v>
+      </c>
+      <c r="I12" s="39" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="34" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B13" s="34" t="inlineStr">
+        <is>
+          <t>fsa:WorkPerformedByEntityAndCapitalised</t>
+        </is>
+      </c>
+      <c r="C13" s="34" t="inlineStr">
+        <is>
+          <t>fsa:WorkPerformedByEntityAndCapitalised</t>
+        </is>
+      </c>
+      <c r="D13" s="35" t="n"/>
+      <c r="E13" s="35" t="n"/>
+      <c r="F13" s="35" t="n"/>
+      <c r="G13" s="35" t="n">
+        <v>-73269</v>
+      </c>
+      <c r="H13" s="35" t="n">
+        <v>-54070</v>
+      </c>
+      <c r="I13" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>
